--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B4FD9B-152E-4432-B3ED-C99A844950E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF7F95D-4F4A-4340-A764-42B4463949A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="202">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -711,10 +711,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,0,0,0,0,0,4,0,0,0,0,0,0,0,0,0,0,0,0,0,3,0,0,0,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>骑兵在森林和小径移动消耗增至10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -780,6 +776,21 @@
   </si>
   <si>
     <t>4846-8/4846-8_7</t>
+  </si>
+  <si>
+    <t>-1,5,5,5,8,12,6,-1,-1,-1,6,4,6,4,5,-1,-1,4,4,4,6,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1,5,4,5,8,12,10,-1,-1,-1,7,4,7,4,5,-1,-1,4,4,4,10,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1,6,5,6,8,12,8,-1,-1,-1,7,4,6,4,5,-1,-1,4,4,4,10,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1,-1,-1,-1,-1,-1,-1,-1,4,4,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1</t>
   </si>
 </sst>
 </file>
@@ -1276,38 +1287,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.26953125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="76.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1386,7 +1397,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1407,7 +1418,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1447,7 +1458,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1528,7 +1539,7 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC3" s="7" t="s">
         <v>177</v>
@@ -1549,7 +1560,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1632,7 +1643,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1653,33 +1664,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I5" s="4">
         <v>30</v>
       </c>
       <c r="J5" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -1713,14 +1724,14 @@
       <c r="AB5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AC5" s="2" t="s">
-        <v>66</v>
+      <c r="AC5" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1730,7 +1741,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1751,7 +1762,7 @@
         <v>95</v>
       </c>
       <c r="H6" s="4">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I6" s="4">
         <v>100</v>
@@ -1795,16 +1806,16 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1814,24 +1825,24 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
       </c>
       <c r="G7" s="4">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H7" s="4">
         <v>105</v>
@@ -1878,16 +1889,16 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1897,18 +1908,18 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1917,7 +1928,7 @@
         <v>85</v>
       </c>
       <c r="H8" s="4">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I8" s="4">
         <v>100</v>
@@ -1964,13 +1975,13 @@
         <v>70</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -1980,7 +1991,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2000,7 +2011,7 @@
         <v>105</v>
       </c>
       <c r="H9" s="4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4">
         <v>100</v>
@@ -2047,16 +2058,16 @@
         <v>176</v>
       </c>
       <c r="AC9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD9" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2066,7 +2077,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2124,8 +2135,8 @@
       <c r="AB10" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AC10" s="2" t="s">
-        <v>66</v>
+      <c r="AC10" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>39</v>
@@ -2135,7 +2146,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2193,8 +2204,8 @@
       <c r="AB11" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AC11" s="2" t="s">
-        <v>66</v>
+      <c r="AC11" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>40</v>
@@ -2204,7 +2215,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2224,7 +2235,7 @@
         <v>70</v>
       </c>
       <c r="H12" s="4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>126</v>
@@ -2264,20 +2275,20 @@
         <v>176</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>140</v>
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2294,10 +2305,10 @@
         <v>139</v>
       </c>
       <c r="G13" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13" s="4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>126</v>
@@ -2340,20 +2351,20 @@
         <v>176</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2370,10 +2381,10 @@
         <v>144</v>
       </c>
       <c r="G14" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H14" s="4">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>126</v>
@@ -2416,20 +2427,20 @@
         <v>176</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2446,10 +2457,10 @@
         <v>164</v>
       </c>
       <c r="G15" s="4">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H15" s="4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>126</v>
@@ -2495,13 +2506,13 @@
         <v>176</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>154</v>
@@ -2511,7 +2522,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2528,10 +2539,10 @@
         <v>163</v>
       </c>
       <c r="G16" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H16" s="4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>126</v>
@@ -2577,13 +2588,13 @@
         <v>176</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>154</v>
@@ -2593,7 +2604,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2613,7 +2624,7 @@
         <v>80</v>
       </c>
       <c r="H17" s="4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>126</v>
@@ -2659,13 +2670,13 @@
         <v>176</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>155</v>
@@ -2675,7 +2686,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2692,10 +2703,10 @@
         <v>121</v>
       </c>
       <c r="G18" s="4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H18" s="4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>126</v>
@@ -2741,13 +2752,13 @@
         <v>176</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>155</v>
@@ -2757,7 +2768,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2796,13 +2807,13 @@
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2841,13 +2852,13 @@
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2886,13 +2897,13 @@
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2931,13 +2942,13 @@
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -2976,13 +2987,13 @@
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3021,13 +3032,13 @@
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3069,13 +3080,13 @@
         <v>176</v>
       </c>
       <c r="AC25" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AD25" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3117,13 +3128,13 @@
         <v>176</v>
       </c>
       <c r="AC26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AD26" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3165,13 +3176,13 @@
         <v>176</v>
       </c>
       <c r="AC27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD27" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AD27" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3213,15 +3224,15 @@
         <v>176</v>
       </c>
       <c r="AC28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD28" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AD28" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3263,12 +3274,12 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3310,10 +3321,10 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3321,7 +3332,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3342,7 +3353,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3363,159 +3374,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF7F95D-4F4A-4340-A764-42B4463949A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F86CC77-E3FA-4634-82E8-FD1496109EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -707,10 +707,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>extraMoveCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>骑兵在森林和小径移动消耗增至10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -791,6 +787,10 @@
   </si>
   <si>
     <t>-1,-1,-1,-1,-1,-1,-1,-1,4,4,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1,-1</t>
+  </si>
+  <si>
+    <t>moveCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1287,38 +1287,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.21875" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.77734375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.88671875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.6640625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.109375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.88671875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1418,7 +1418,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1539,10 +1539,10 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7" t="s">
@@ -1560,7 +1560,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1664,18 +1664,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -1725,13 +1725,13 @@
         <v>70</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1806,16 +1806,16 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1825,18 +1825,18 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
@@ -1889,16 +1889,16 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1908,18 +1908,18 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1975,13 +1975,13 @@
         <v>70</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2058,16 +2058,16 @@
         <v>176</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>176</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>39</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>176</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>40</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2275,20 +2275,20 @@
         <v>176</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>140</v>
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2351,20 +2351,20 @@
         <v>176</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2427,20 +2427,20 @@
         <v>176</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2506,13 +2506,13 @@
         <v>176</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>154</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2588,13 +2588,13 @@
         <v>176</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>154</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2670,13 +2670,13 @@
         <v>176</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>155</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2752,13 +2752,13 @@
         <v>176</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>155</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2807,13 +2807,13 @@
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2852,13 +2852,13 @@
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2897,13 +2897,13 @@
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2942,13 +2942,13 @@
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -2987,13 +2987,13 @@
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3032,13 +3032,13 @@
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3080,13 +3080,13 @@
         <v>176</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3128,13 +3128,13 @@
         <v>176</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3176,13 +3176,13 @@
         <v>176</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3224,15 +3224,15 @@
         <v>176</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3274,12 +3274,12 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3321,10 +3321,10 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3332,7 +3332,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3353,7 +3353,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3374,159 +3374,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F86CC77-E3FA-4634-82E8-FD1496109EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0B42F9-F276-47C2-8E94-8A84C459AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -601,14 +601,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>冲车</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -633,10 +625,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -790,6 +778,18 @@
   </si>
   <si>
     <t>moveCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1287,38 +1287,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.21875" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.77734375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.88671875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.6640625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.109375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>64</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>110</v>
@@ -1397,7 +1397,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1418,7 +1418,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1497,13 +1497,13 @@
         <v>73</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>108</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>96</v>
@@ -1539,10 +1539,10 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7" t="s">
@@ -1560,7 +1560,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1664,18 +1664,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -1725,13 +1725,13 @@
         <v>70</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1780,7 +1780,7 @@
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>146</v>
@@ -1806,16 +1806,16 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1825,18 +1825,18 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
@@ -1863,7 +1863,7 @@
         <v>67</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>149</v>
@@ -1889,16 +1889,16 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1908,18 +1908,18 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1946,7 +1946,7 @@
         <v>68</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>148</v>
@@ -1975,13 +1975,13 @@
         <v>70</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>69</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>147</v>
@@ -2055,19 +2055,19 @@
         <v>53</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2133,10 +2133,10 @@
         <v>53</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>39</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2202,10 +2202,10 @@
         <v>53</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>40</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2246,10 +2246,10 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -2272,23 +2272,23 @@
         <v>54</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>140</v>
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2319,13 +2319,13 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -2348,23 +2348,23 @@
         <v>54</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2395,13 +2395,13 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -2424,37 +2424,37 @@
         <v>54</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15" s="4">
         <v>8</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G15" s="4">
         <v>90</v>
@@ -2474,13 +2474,13 @@
         <v>70</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -2503,40 +2503,40 @@
         <v>53</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D16" s="4">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G16" s="4">
         <v>100</v>
@@ -2556,13 +2556,13 @@
         <v>70</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -2585,26 +2585,26 @@
         <v>53</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2615,10 +2615,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G17" s="4">
         <v>80</v>
@@ -2638,13 +2638,13 @@
         <v>70</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -2667,26 +2667,26 @@
         <v>53</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AH17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>121</v>
@@ -2720,13 +2720,13 @@
         <v>70</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -2749,26 +2749,26 @@
         <v>53</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2795,25 +2795,25 @@
         <v>126</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O19" s="4">
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2840,25 +2840,25 @@
         <v>125</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O20" s="4">
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2885,25 +2885,25 @@
         <v>125</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O21" s="4">
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2930,25 +2930,25 @@
         <v>126</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O22" s="4">
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -2975,25 +2975,25 @@
         <v>125</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O23" s="4">
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3020,25 +3020,25 @@
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O24" s="4">
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3071,22 +3071,22 @@
         <v>69</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O25" s="4">
         <v>11</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3119,27 +3119,27 @@
         <v>69</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O26" s="4">
         <v>14</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
@@ -3167,22 +3167,22 @@
         <v>69</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O27" s="4">
         <v>15</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3215,24 +3215,24 @@
         <v>69</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O28" s="4">
         <v>17</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3259,13 +3259,13 @@
         <v>125</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>121</v>
@@ -3274,12 +3274,12 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3306,13 +3306,13 @@
         <v>125</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>122</v>
@@ -3321,10 +3321,10 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3332,7 +3332,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3353,7 +3353,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3374,159 +3374,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0B42F9-F276-47C2-8E94-8A84C459AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3516A5-8723-4BC9-A5C7-DB4D148CEE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31080" yWindow="1185" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="204">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -625,14 +625,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>木兽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -790,6 +782,22 @@
   </si>
   <si>
     <t>8,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-23</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1355,7 +1363,7 @@
         <v>64</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>110</v>
@@ -1397,7 +1405,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1497,13 +1505,13 @@
         <v>73</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>108</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>96</v>
@@ -1539,10 +1547,10 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7" t="s">
@@ -1643,7 +1651,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1669,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -1725,13 +1733,13 @@
         <v>70</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1780,7 +1788,7 @@
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>146</v>
@@ -1806,16 +1814,16 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1830,13 +1838,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
@@ -1863,7 +1871,7 @@
         <v>67</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>149</v>
@@ -1889,16 +1897,16 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1913,13 +1921,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1946,7 +1954,7 @@
         <v>68</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>148</v>
@@ -1975,13 +1983,13 @@
         <v>70</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -2029,7 +2037,7 @@
         <v>69</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>147</v>
@@ -2055,19 +2063,19 @@
         <v>53</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2133,10 +2141,10 @@
         <v>53</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>39</v>
@@ -2202,10 +2210,10 @@
         <v>53</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>40</v>
@@ -2246,10 +2254,10 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -2272,16 +2280,16 @@
         <v>54</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>140</v>
@@ -2319,13 +2327,13 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -2348,16 +2356,16 @@
         <v>54</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>141</v>
@@ -2395,13 +2403,13 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -2424,16 +2432,16 @@
         <v>54</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>142</v>
@@ -2454,7 +2462,7 @@
         <v>150</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G15" s="4">
         <v>90</v>
@@ -2474,13 +2482,13 @@
         <v>70</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -2503,16 +2511,16 @@
         <v>53</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>152</v>
@@ -2527,7 +2535,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D16" s="4">
         <v>8</v>
@@ -2536,7 +2544,7 @@
         <v>150</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G16" s="4">
         <v>100</v>
@@ -2556,13 +2564,13 @@
         <v>70</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -2585,16 +2593,16 @@
         <v>53</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>152</v>
@@ -2618,7 +2626,7 @@
         <v>151</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G17" s="4">
         <v>80</v>
@@ -2638,10 +2646,10 @@
         <v>70</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>155</v>
@@ -2667,16 +2675,16 @@
         <v>53</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>153</v>
@@ -2720,10 +2728,10 @@
         <v>70</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>155</v>
@@ -2749,16 +2757,16 @@
         <v>53</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>153</v>
@@ -2795,22 +2803,22 @@
         <v>126</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O19" s="4">
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="2:35" x14ac:dyDescent="0.15">
@@ -2840,22 +2848,22 @@
         <v>125</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O20" s="4">
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="2:35" x14ac:dyDescent="0.15">
@@ -2885,22 +2893,22 @@
         <v>125</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O21" s="4">
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="2:35" x14ac:dyDescent="0.15">
@@ -2930,22 +2938,22 @@
         <v>126</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O22" s="4">
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="2:35" x14ac:dyDescent="0.15">
@@ -2975,22 +2983,22 @@
         <v>125</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O23" s="4">
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="2:35" x14ac:dyDescent="0.15">
@@ -3020,22 +3028,22 @@
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O24" s="4">
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="2:35" x14ac:dyDescent="0.15">
@@ -3071,19 +3079,19 @@
         <v>69</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O25" s="4">
         <v>11</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:35" x14ac:dyDescent="0.15">
@@ -3119,19 +3127,19 @@
         <v>69</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O26" s="4">
         <v>14</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:35" x14ac:dyDescent="0.15">
@@ -3167,19 +3175,19 @@
         <v>69</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O27" s="4">
         <v>15</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.15">
@@ -3215,19 +3223,19 @@
         <v>69</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O28" s="4">
         <v>17</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
@@ -3259,13 +3267,13 @@
         <v>125</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>121</v>
@@ -3274,7 +3282,7 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
@@ -3306,13 +3314,13 @@
         <v>125</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>122</v>
@@ -3321,7 +3329,7 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="2:35" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3516A5-8723-4BC9-A5C7-DB4D148CEE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C36D60-4F66-469B-A3D1-34B8FBE7C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31080" yWindow="1185" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -1295,38 +1295,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1426,7 +1426,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>54</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3240,7 +3240,7 @@
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3340,7 +3340,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3361,7 +3361,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3382,159 +3382,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C36D60-4F66-469B-A3D1-34B8FBE7C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48C5AAC-DD11-45EB-92F3-5191CE118D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="204">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1295,38 +1295,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1426,7 +1426,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2331,6 +2331,9 @@
       </c>
       <c r="N13" s="2" t="s">
         <v>168</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>198</v>
@@ -2372,7 +2375,7 @@
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2407,6 +2410,9 @@
       </c>
       <c r="N14" s="2" t="s">
         <v>168</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>199</v>
@@ -2448,7 +2454,7 @@
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2530,7 +2536,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2612,7 +2618,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2694,7 +2700,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2776,7 +2782,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2821,7 +2827,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2866,7 +2872,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2911,7 +2917,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2956,7 +2962,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3001,7 +3007,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3046,7 +3052,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3094,7 +3100,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3142,7 +3148,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3190,7 +3196,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3240,7 +3246,7 @@
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3287,7 +3293,7 @@
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3332,7 +3338,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3340,7 +3346,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3361,7 +3367,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3382,159 +3388,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48C5AAC-DD11-45EB-92F3-5191CE118D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65676CDA-A7AB-440C-8A61-11193C6617BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="204">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1295,38 +1295,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7265625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1426,7 +1426,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2098,9 +2098,11 @@
       <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="18"/>
+      <c r="F10" s="18" t="s">
+        <v>65</v>
+      </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4">
         <v>50</v>
@@ -2154,7 +2156,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2167,9 +2169,11 @@
       <c r="E11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="18"/>
+      <c r="F11" s="18" t="s">
+        <v>65</v>
+      </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4">
         <v>50</v>
@@ -2223,7 +2227,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2296,7 +2300,7 @@
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2375,7 +2379,7 @@
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2536,7 +2540,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2618,7 +2622,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2782,7 +2786,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2827,7 +2831,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2872,7 +2876,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2917,7 +2921,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2962,7 +2966,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3007,7 +3011,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3052,7 +3056,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3100,7 +3104,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3196,7 +3200,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3246,7 +3250,7 @@
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3293,7 +3297,7 @@
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3338,7 +3342,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3346,7 +3350,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3367,7 +3371,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3388,159 +3392,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65676CDA-A7AB-440C-8A61-11193C6617BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3553DAF-F576-4270-8790-9B6165A77BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -1295,38 +1295,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7265625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" style="2" customWidth="1"/>
+    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1426,7 +1426,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>50</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4">
         <v>25</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>50</v>
       </c>
       <c r="I11" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4">
         <v>28</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3250,7 +3250,7 @@
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3350,7 +3350,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3371,7 +3371,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3392,159 +3392,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3553DAF-F576-4270-8790-9B6165A77BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7E2610-1E18-4C76-A879-5B98457BA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="205">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -798,6 +798,10 @@
   </si>
   <si>
     <t>-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1295,38 +1299,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.75" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7265625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1426,7 +1430,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,7 +1470,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1568,7 +1572,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1676,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1833,7 +1837,7 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1999,7 +2003,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2156,7 +2160,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2227,7 +2231,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2379,7 +2383,7 @@
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2540,7 +2544,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2622,7 +2626,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2645,7 +2649,7 @@
         <v>85</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="J17" s="4">
         <v>18</v>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2786,7 +2790,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2831,7 +2835,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2876,7 +2880,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2921,7 +2925,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2966,7 +2970,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3011,7 +3015,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3056,7 +3060,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3104,7 +3108,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3152,7 +3156,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3250,7 +3254,7 @@
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3297,7 +3301,7 @@
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3342,7 +3346,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3350,7 +3354,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3371,7 +3375,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3392,159 +3396,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>
